--- a/New folder/(RM)Raw_Material_Purchase_Oder_Planning/GTG_daily_stock_analysis/Item_wise_order_calculation_per_month_in_kg_CONNECTED/temp_out_of_monthly_5.xlsx
+++ b/New folder/(RM)Raw_Material_Purchase_Oder_Planning/GTG_daily_stock_analysis/Item_wise_order_calculation_per_month_in_kg_CONNECTED/temp_out_of_monthly_5.xlsx
@@ -492,7 +492,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>844.3728</v>
+        <v>790.6211999999999</v>
       </c>
       <c r="C6" t="n">
         <v>47.832</v>
@@ -505,10 +505,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24862.536932</v>
+        <v>23628.024032</v>
       </c>
       <c r="C7" t="n">
-        <v>2430.35088</v>
+        <v>2366.59362</v>
       </c>
     </row>
     <row r="8">
@@ -518,7 +518,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>755.013513</v>
+        <v>742.4083529999999</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
